--- a/Gestao/painel_risco_certifaied.xlsx
+++ b/Gestao/painel_risco_certifaied.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Painel de Risco Ético" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Painel de Risco Ético" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,26 +28,50 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A237E"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="000044BB"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F497D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="007030A0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="004B0082"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B25900"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -56,26 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E88E5"/>
-        <bgColor rgb="001E88E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
-        <bgColor rgb="00FFEBEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
-        <bgColor rgb="00FFFDE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-        <bgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,16 +95,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0BEC5"/>
+        <color rgb="00B0C4DE"/>
       </left>
       <right style="thin">
-        <color rgb="00B0BEC5"/>
+        <color rgb="00B0C4DE"/>
       </right>
       <top style="thin">
-        <color rgb="00B0BEC5"/>
+        <color rgb="00B0C4DE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0BEC5"/>
+        <color rgb="00B0C4DE"/>
       </bottom>
     </border>
   </borders>
@@ -107,32 +113,26 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,312 +499,248 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PAINEL DE AVALIAÇÃO DE RISCO ÉTICO (CERTIFAIEd)</t>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Ético</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Definição / Contexto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Parte Interessada</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Intensidade</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Probabilidade</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Score Risco</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista ordenada do Maior Risco (Crítico) ao Menor Risco (Mitigado)</t>
-        </is>
+          <t>🔴 (Alto)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Privacidade</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>os dados dos clientes devem estar protegidos pela LGPD</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Desenvolvedores</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Aumenta</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>🟡 (Médio)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Transparência</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>os emails devem ser classificados segundo regras claras para clientes e colaboradores</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Clientes externo</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Minimiza</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Status Risco</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>🟡 (Médio)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Valor Ético</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Definição / Contexto do AIS</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Parte Interessada</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Intensidade</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Probabilidade</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Score de Risco</t>
-        </is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Transparência</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>a classificacao deve ser clara para os colaboradores</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Clientes interno</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Minimiza</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>🔴  ALTO</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>R001</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Transparência</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Sistema de diálogo informa detalhes de seu funcionamento</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>🟢 (Baixo)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Solidariedade</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>o sistema deve ser solidario com as pessoas</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Clientes externo</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Aumenta</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>🟡  MÉDIO</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Privacidade</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Pessoas podem informar dados pessoais. O chatbot deve descartar</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Clientes externo</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Aumenta</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>🟢  BAIXO</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Justiça</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Nos diálogos trata as pessoas por sr e sra evitando linguagem ofensiva</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Clientes externo</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+          <t>Sociedade / Geral</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Minimiza</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>🟢  BAIXO</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Não-maleficência</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Sistema previne respostas com desinformação ou preconceito</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Desenvolvedores</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Minimiza</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>🟢  BAIXO</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Privacidade</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>o sistema garante o sigilo dos dados</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Clientes externos</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Minimiza</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>-2</v>
+      <c r="I5" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>